--- a/tumores/5. Laringe.xlsx
+++ b/tumores/5. Laringe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\Proyecto Practicas\tumores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF172F6-F680-452B-AA8F-5B675895B5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96E1398-8292-4C35-B299-06F5BB824656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14520" yWindow="0" windowWidth="8520" windowHeight="8880" activeTab="1" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
   <sheets>
     <sheet name="TNM" sheetId="1" r:id="rId1"/>
@@ -109,12 +109,6 @@
     <t>Ganglio ipsilateral ≤3 cm y ENE-</t>
   </si>
   <si>
-    <t>Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
-  </si>
-  <si>
-    <t>Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>≤3 cm y ENE+, &gt;3 cm pero ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -127,9 +121,6 @@
     <t>Ganglio ipsilateral &gt;3 cm ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>Múltiples ganglios ipsilaterales ≤6 cm</t>
-  </si>
-  <si>
     <t>Ganglio ipsilateral &gt;6 cm y ENE-</t>
   </si>
   <si>
@@ -148,21 +139,6 @@
     <t>Tipo</t>
   </si>
   <si>
-    <t>Ganglios contralaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Ganglios bilaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Contralaterales ≤6 cm y ENE-</t>
-  </si>
-  <si>
-    <t>Bilaterales ≤6 cm y ENE-</t>
-  </si>
-  <si>
-    <t>Un ganglio ipsilateral &gt;3 cm , Multiples ganglios, Un solo ganglio contralateral de cualquier tamaño</t>
-  </si>
-  <si>
     <t>Sin metástasis</t>
   </si>
   <si>
@@ -223,18 +199,12 @@
     <t>Mucosa de la base de la lengua, Valécula, Pared media del seno piriforme</t>
   </si>
   <si>
-    <t>Invasion sin fijacion de laringe:</t>
-  </si>
-  <si>
     <t> Area poscricoidea, Espacio preepiglótico, Espacio paraglótico, Corteza interna del cartílago tiroides</t>
   </si>
   <si>
     <t>Invasión:</t>
   </si>
   <si>
-    <t>Fijación de una c.vocal</t>
-  </si>
-  <si>
     <t>Invasión corteza externa del cartílago tiroides</t>
   </si>
   <si>
@@ -259,12 +229,6 @@
     <t>Movilidad normal, Movilidad deteriorada</t>
   </si>
   <si>
-    <t>Ambas c.vocales +</t>
-  </si>
-  <si>
-    <t>Una c.vocal +</t>
-  </si>
-  <si>
     <t>Fijación de una cuerda vocal, Invasión del espacio paraglótico, Invasión de la corteza interna del cartílago tiroides</t>
   </si>
   <si>
@@ -277,9 +241,6 @@
     <t>T1b</t>
   </si>
   <si>
-    <t>Diseminacion a supraglotis, Diseminacion a subglotis</t>
-  </si>
-  <si>
     <t>Deterioro de ambas cuerdas</t>
   </si>
   <si>
@@ -301,12 +262,6 @@
     <t>Ganglio ipsilat.</t>
   </si>
   <si>
-    <t>Limitado a una cuerda vocal mov. normal</t>
-  </si>
-  <si>
-    <t>Afectacion ambas cuerdas vocales mov. Normal</t>
-  </si>
-  <si>
     <t>TX: Tumor primario no evaluable</t>
   </si>
   <si>
@@ -355,21 +310,12 @@
     <t>🟦T3: Invasion especifica *</t>
   </si>
   <si>
-    <t>🟨T2: Invasion fuera de supraglotis sin fijacion de la laringe *</t>
-  </si>
-  <si>
     <t>🟨T2: Invasión en más de un subsitio</t>
   </si>
   <si>
     <t>🟩T1: Limitado a subglotis</t>
   </si>
   <si>
-    <t>🟨T2: Diseminacion a una cuerda vocal *</t>
-  </si>
-  <si>
-    <t>🟨T2: Diseminacion de ambas cuerdas vocales *</t>
-  </si>
-  <si>
     <t>🟥T4a: Invasión de tejidos fuera de la laringe *</t>
   </si>
   <si>
@@ -385,9 +331,6 @@
     <t>🟨 N2a: Un ganglio ipsilateral &gt;3 cm pero ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟨N2b: Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
-  </si>
-  <si>
     <t>🟨N2c: Ganglios contralaterales ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -397,9 +340,6 @@
     <t>🟦N3a: Un ganglio ipsilateral &gt;6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟦 N3b: Un ganglios con ENE+</t>
-  </si>
-  <si>
     <t>🟦N3b: Más de un ganglio con ENE+</t>
   </si>
   <si>
@@ -424,7 +364,67 @@
     <t>🟩T1: Limitado a un subsitio con movilidad normal de cuerdas vocales</t>
   </si>
   <si>
-    <t>🟦T3: Limitado a la laringe con fijacion de una cuerda vocal</t>
+    <t>🟨T2: Invasión fuera de supraglotis sin fijación de la laringe *</t>
+  </si>
+  <si>
+    <t>Invasión sin fijación de laringe:</t>
+  </si>
+  <si>
+    <t>🟦T3: Limitado a la laringe con fijación de una cuerda vocal</t>
+  </si>
+  <si>
+    <t>Limitado laringe + Fijación de una c.vocal</t>
+  </si>
+  <si>
+    <t>Limitado a una cuerda vocal, mov. normal</t>
+  </si>
+  <si>
+    <t>Afectación de ambas cuerdas vocales, mov. normal</t>
+  </si>
+  <si>
+    <t>Diseminación a supraglotis, Diseminación a subglotis</t>
+  </si>
+  <si>
+    <t>🟨T2: Diseminación a una cuerda vocal *</t>
+  </si>
+  <si>
+    <t>🟨T2: Diseminación de ambas cuerdas vocales *</t>
+  </si>
+  <si>
+    <t>Disem. Una c.vocal +</t>
+  </si>
+  <si>
+    <t>Disem. Ambas c.vocales +</t>
+  </si>
+  <si>
+    <t>🟨N2b: Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios bilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios contralaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟦 N3b: Un ganglio con ENE+</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>G.Contralaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>G.Bilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Un ganglio ipsilateral &gt;3 cm , Múltiples ganglios, Un solo ganglio contralateral de cualquier tamaño</t>
   </si>
 </sst>
 </file>
@@ -957,10 +957,10 @@
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>9</v>
@@ -969,7 +969,7 @@
         <v>12</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>10</v>
@@ -980,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>1</v>
@@ -997,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>2</v>
@@ -1014,16 +1014,16 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1031,16 +1031,16 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1048,19 +1048,19 @@
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1068,16 +1068,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1085,19 +1085,19 @@
         <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1105,16 +1105,16 @@
         <v>0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1122,19 +1122,19 @@
         <v>0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1142,16 +1142,16 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1159,16 +1159,16 @@
         <v>0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1176,18 +1176,18 @@
         <v>0</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1195,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>1</v>
@@ -1212,10 +1212,10 @@
         <v>0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>2</v>
@@ -1229,16 +1229,16 @@
         <v>0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1246,16 +1246,16 @@
         <v>0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1263,19 +1263,19 @@
         <v>0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="72" x14ac:dyDescent="0.3">
@@ -1283,19 +1283,19 @@
         <v>0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1303,16 +1303,16 @@
         <v>0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1320,19 +1320,19 @@
         <v>0</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1340,16 +1340,16 @@
         <v>0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1357,16 +1357,16 @@
         <v>0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1374,18 +1374,18 @@
         <v>0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1393,11 +1393,11 @@
         <v>0</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="13" t="s">
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>2</v>
@@ -1429,16 +1429,16 @@
         <v>0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -1446,19 +1446,19 @@
         <v>0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1466,19 +1466,19 @@
         <v>0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="72" x14ac:dyDescent="0.3">
@@ -1486,19 +1486,19 @@
         <v>0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1523,19 +1523,19 @@
         <v>0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1543,16 +1543,16 @@
         <v>0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1560,16 +1560,16 @@
         <v>0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1577,18 +1577,18 @@
         <v>0</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1600,7 +1600,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
@@ -1619,14 +1619,14 @@
         <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1638,7 +1638,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
@@ -1657,14 +1657,14 @@
         <v>15</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1675,13 +1675,13 @@
         <v>15</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1692,13 +1692,13 @@
         <v>15</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1709,13 +1709,13 @@
         <v>15</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1726,13 +1726,13 @@
         <v>15</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1740,14 +1740,14 @@
         <v>15</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -1759,14 +1759,14 @@
         <v>15</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -1777,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>17</v>
@@ -1794,13 +1794,13 @@
         <v>16</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1811,7 +1811,7 @@
         <v>16</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>19</v>
@@ -1828,16 +1828,16 @@
         <v>16</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1848,13 +1848,13 @@
         <v>16</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1865,13 +1865,13 @@
         <v>16</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -1882,13 +1882,13 @@
         <v>16</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -1899,13 +1899,13 @@
         <v>16</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1917,44 +1917,44 @@
         <v>16</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1980,24 +1980,24 @@
         <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2008,10 +2008,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -2022,24 +2022,24 @@
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -2047,41 +2047,41 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -2089,27 +2089,27 @@
         <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -2120,7 +2120,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>

--- a/tumores/5. Laringe.xlsx
+++ b/tumores/5. Laringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96E1398-8292-4C35-B299-06F5BB824656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE95C42-ADD6-4619-AA1C-9BE5CFADA38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="132">
   <si>
     <t>T</t>
   </si>
@@ -281,9 +281,6 @@
   </si>
   <si>
     <t>🟩T1a: Limitado a una cuerda vocal (movilidad normal)</t>
-  </si>
-  <si>
-    <t>🟥T4a: Invasión de tejidos fuera de la laringe</t>
   </si>
   <si>
     <t>🟥T4b: Invasión del espacio prevertebral</t>
@@ -1017,7 +1014,7 @@
         <v>51</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>3</v>
@@ -1034,7 +1031,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>4</v>
@@ -1051,7 +1048,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>56</v>
@@ -1060,7 +1057,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1071,13 +1068,13 @@
         <v>51</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -1088,7 +1085,7 @@
         <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>57</v>
@@ -1108,7 +1105,7 @@
         <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>7</v>
@@ -1238,7 +1235,7 @@
         <v>69</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1249,13 +1246,13 @@
         <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>70</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1266,10 +1263,10 @@
         <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>4</v>
@@ -1286,7 +1283,7 @@
         <v>52</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>67</v>
@@ -1306,7 +1303,7 @@
         <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>7</v>
@@ -1323,7 +1320,7 @@
         <v>52</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>60</v>
@@ -1343,7 +1340,7 @@
         <v>52</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>13</v>
@@ -1360,7 +1357,7 @@
         <v>52</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>13</v>
@@ -1378,7 +1375,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6" t="s">
@@ -1432,7 +1429,7 @@
         <v>53</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>3</v>
@@ -1449,7 +1446,7 @@
         <v>53</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>66</v>
@@ -1458,7 +1455,7 @@
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1469,7 +1466,7 @@
         <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>66</v>
@@ -1478,7 +1475,7 @@
         <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="72" x14ac:dyDescent="0.3">
@@ -1489,7 +1486,7 @@
         <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>67</v>
@@ -1509,7 +1506,7 @@
         <v>53</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>7</v>
@@ -1526,7 +1523,7 @@
         <v>53</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>60</v>
@@ -1546,7 +1543,7 @@
         <v>53</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>13</v>
@@ -1563,7 +1560,7 @@
         <v>53</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>13</v>
@@ -1581,7 +1578,7 @@
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4" t="s">
@@ -1600,7 +1597,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
@@ -1619,7 +1616,7 @@
         <v>15</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
@@ -1638,7 +1635,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
@@ -1657,7 +1654,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
@@ -1675,13 +1672,13 @@
         <v>15</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1692,13 +1689,13 @@
         <v>15</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1709,13 +1706,13 @@
         <v>15</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1726,7 +1723,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>23</v>
@@ -1740,7 +1737,7 @@
         <v>15</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6" t="s">
@@ -1759,7 +1756,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6" t="s">
@@ -1777,7 +1774,7 @@
         <v>16</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>17</v>
@@ -1794,7 +1791,7 @@
         <v>16</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>18</v>
@@ -1811,7 +1808,7 @@
         <v>16</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>19</v>
@@ -1828,7 +1825,7 @@
         <v>16</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>27</v>
@@ -1848,13 +1845,13 @@
         <v>16</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1865,13 +1862,13 @@
         <v>16</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -1882,13 +1879,13 @@
         <v>16</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -1899,13 +1896,13 @@
         <v>16</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1917,10 +1914,10 @@
         <v>16</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>24</v>
@@ -1934,7 +1931,7 @@
         <v>32</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>33</v>
@@ -1948,7 +1945,7 @@
         <v>32</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>34</v>

--- a/tumores/5. Laringe.xlsx
+++ b/tumores/5. Laringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE95C42-ADD6-4619-AA1C-9BE5CFADA38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB9B5EF-E7CB-4C9E-80A5-C95274E59034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
